--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA168"/>
+  <dimension ref="A1:AA169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17921,6 +17921,87 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>46975</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>11905 Avenida Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>8010314</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>contacto@comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2528 0260</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr"/>
+      <c r="R169" s="2" t="inlineStr"/>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pamacriclaudioarrauconlosmorros/</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.instagram.com/pamacrilosmorros/</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr"/>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA169"/>
+  <dimension ref="A1:AA170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18002,6 +18002,87 @@
       <c r="Z169" s="2" t="inlineStr"/>
       <c r="AA169" s="2" t="inlineStr"/>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>46975</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>11905 Avenida Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>8010314</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>contacto@comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2528 0260</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr"/>
+      <c r="R170" s="2" t="inlineStr"/>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pamacriclaudioarrauconlosmorros/</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.instagram.com/pamacrilosmorros/</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr"/>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA170"/>
+  <dimension ref="A1:AA172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18083,6 +18083,172 @@
       <c r="Z170" s="2" t="inlineStr"/>
       <c r="AA170" s="2" t="inlineStr"/>
     </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Comercial Serotrade Chile Limitada</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Outlet del Vino</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>29634</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Av. Lo Espejo 943, Local 196</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>9250000</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.outletdelvino.com</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>contacto@outletdelvino.com</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2821 0160</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>76068631K</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr"/>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>46975</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>11905 Avenida Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>8010314</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>contacto@comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2528 0260</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pamacriclaudioarrauconlosmorros/</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.instagram.com/pamacrilosmorros/</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr"/>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Chile.xlsx
+++ b/BWI/bestwine_output/bestwine_Chile.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA172"/>
+  <dimension ref="A1:AA174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18249,6 +18249,172 @@
       <c r="Z172" s="2" t="inlineStr"/>
       <c r="AA172" s="2" t="inlineStr"/>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Comercial Serotrade Chile Limitada</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Outlet del Vino</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>29634</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Av. Lo Espejo 943, Local 196</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>9250000</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.outletdelvino.com</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>contacto@outletdelvino.com</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2821 0160</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>76068631K</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr"/>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Pamacri Los Morros</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>46975</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>El Bosque</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Región Metropolitana, Santiago</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>11905 Avenida Padre Hurtado</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>8010314</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>contacto@comercialpamacri.cl</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>+56 2 2528 0260</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr"/>
+      <c r="R174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pamacriclaudioarrauconlosmorros/</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.instagram.com/pamacrilosmorros/</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr"/>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
